--- a/erp-server/erp-server-file/src/main/resources/excel/wms/overseasDeliveryPlan.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/overseasDeliveryPlan.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>单据编号</t>
   </si>
@@ -56,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>平台(第三方仓)</t>
     </r>
     <r>
@@ -85,6 +92,15 @@
   </si>
   <si>
     <t>发货数量</t>
+  </si>
+  <si>
+    <t>期望发货时间</t>
+  </si>
+  <si>
+    <t>期望物流方式</t>
+  </si>
+  <si>
+    <t>来源单号</t>
   </si>
   <si>
     <t>创建人</t>
@@ -145,6 +161,15 @@
   </si>
   <si>
     <t>{.deliveryQty}</t>
+  </si>
+  <si>
+    <t>{.expectDeliveryDate}</t>
+  </si>
+  <si>
+    <t>{.expectLogisticsMethodName}</t>
+  </si>
+  <si>
+    <t>{.sourceCodes}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1180,7 +1205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:WPP2"/>
+  <dimension ref="A1:WPS2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1196,14 +1221,17 @@
     <col min="13" max="13" width="31.5" customWidth="1"/>
     <col min="14" max="14" width="10.25" customWidth="1"/>
     <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="17" width="10.25" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
-    <col min="19" max="19" width="17.25" customWidth="1"/>
-    <col min="20" max="20" width="18.375" customWidth="1"/>
-    <col min="21" max="224" width="9" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5" customWidth="1"/>
+    <col min="17" max="17" width="17.875" customWidth="1"/>
+    <col min="18" max="18" width="19.625" customWidth="1"/>
+    <col min="19" max="20" width="10.25" customWidth="1"/>
+    <col min="21" max="21" width="9.625" customWidth="1"/>
+    <col min="22" max="22" width="17.25" customWidth="1"/>
+    <col min="23" max="23" width="18.375" customWidth="1"/>
+    <col min="24" max="227" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:23">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1264,71 +1292,86 @@
       <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:15980">
-      <c r="A2" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:15983">
+      <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
+      <c r="R2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
@@ -17286,6 +17329,9 @@
       <c r="WPN2" s="4"/>
       <c r="WPO2" s="4"/>
       <c r="WPP2" s="4"/>
+      <c r="WPQ2" s="4"/>
+      <c r="WPR2" s="4"/>
+      <c r="WPS2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/overseasDeliveryPlan.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/overseasDeliveryPlan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>单据编号</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>单据类型</t>
+  </si>
+  <si>
+    <t>发货类型</t>
   </si>
   <si>
     <t>店铺名称</t>
@@ -131,6 +134,9 @@
   </si>
   <si>
     <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.deliveryTypeName}</t>
   </si>
   <si>
     <t>{.shopName}</t>
@@ -1205,33 +1211,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:WPS2"/>
+  <dimension ref="A1:WPT2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="6" width="12.375" customWidth="1"/>
-    <col min="7" max="7" width="24.125" customWidth="1"/>
-    <col min="8" max="8" width="7.375" customWidth="1"/>
-    <col min="9" max="9" width="16.375" customWidth="1"/>
-    <col min="10" max="10" width="17.5" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="12" max="12" width="14.375" customWidth="1"/>
-    <col min="13" max="13" width="31.5" customWidth="1"/>
-    <col min="14" max="14" width="10.25" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="17.5" customWidth="1"/>
-    <col min="17" max="17" width="17.875" customWidth="1"/>
-    <col min="18" max="18" width="19.625" customWidth="1"/>
-    <col min="19" max="20" width="10.25" customWidth="1"/>
-    <col min="21" max="21" width="9.625" customWidth="1"/>
-    <col min="22" max="22" width="17.25" customWidth="1"/>
-    <col min="23" max="23" width="18.375" customWidth="1"/>
-    <col min="24" max="227" width="9" hidden="1" customWidth="1"/>
+    <col min="4" max="7" width="12.375" customWidth="1"/>
+    <col min="8" max="8" width="24.125" customWidth="1"/>
+    <col min="9" max="9" width="7.375" customWidth="1"/>
+    <col min="10" max="10" width="16.375" customWidth="1"/>
+    <col min="11" max="11" width="17.5" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="14.375" customWidth="1"/>
+    <col min="14" max="14" width="31.5" customWidth="1"/>
+    <col min="15" max="15" width="10.25" customWidth="1"/>
+    <col min="16" max="16" width="9.5" customWidth="1"/>
+    <col min="17" max="17" width="17.5" customWidth="1"/>
+    <col min="18" max="18" width="17.875" customWidth="1"/>
+    <col min="19" max="19" width="19.625" customWidth="1"/>
+    <col min="20" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="17.25" customWidth="1"/>
+    <col min="24" max="24" width="18.375" customWidth="1"/>
+    <col min="25" max="228" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1253,10 +1259,10 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1265,7 +1271,7 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
@@ -1301,78 +1307,83 @@
       <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:15983">
-      <c r="A2" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:15984">
+      <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="4"/>
+      <c r="W2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
@@ -17332,6 +17343,7 @@
       <c r="WPQ2" s="4"/>
       <c r="WPR2" s="4"/>
       <c r="WPS2" s="4"/>
+      <c r="WPT2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
